--- a/downloads/Trainory_NIST_CSF_2_Assessment.xlsx
+++ b/downloads/Trainory_NIST_CSF_2_Assessment.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CSF Assessment" sheetId="1" r:id="R271a31e2e05944d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework Guide" sheetId="2" r:id="R4292c77f0c2e4efd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CSF Assessment" sheetId="1" r:id="Rdfda464badf54516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Framework Guide" sheetId="2" r:id="R6ded6aa4ca654586"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="14">
+  <x:fonts count="15">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -94,8 +94,14 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -120,6 +126,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF7FAFC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF193B5B"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -229,7 +265,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="90">
+  <x:cellXfs count="97">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -422,6 +458,13 @@
     <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -433,7 +476,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -444,7 +487,7 @@
         <x:color rgb="FF7A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -455,7 +498,7 @@
         <x:color rgb="FF842029"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -466,7 +509,7 @@
         <x:color rgb="FF166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFDFF3E4"/>
         </x:patternFill>
       </x:fill>
@@ -477,7 +520,7 @@
         <x:color rgb="FF7A5A00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF4D6"/>
         </x:patternFill>
       </x:fill>
@@ -488,7 +531,7 @@
         <x:color rgb="FF842029"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -499,7 +542,7 @@
         <x:color rgb="FF842029"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF8D7DA"/>
         </x:patternFill>
       </x:fill>
@@ -510,7 +553,7 @@
         <x:color rgb="FF9A4D00"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4C5"/>
         </x:patternFill>
       </x:fill>
@@ -779,23 +822,53 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4" t="str">
-        <x:v>Step 4 | Selected cybersecurity outcomes based on Trainory's approved risks and scope</x:v>
-      </x:c>
-      <x:c r="B2" s="4"/>
-      <x:c r="C2" s="4"/>
-      <x:c r="D2" s="4"/>
-      <x:c r="E2" s="4"/>
-      <x:c r="F2" s="4"/>
-      <x:c r="G2" s="4"/>
-      <x:c r="H2" s="4"/>
-      <x:c r="I2" s="4"/>
-      <x:c r="J2" s="4"/>
-      <x:c r="K2" s="4"/>
-      <x:c r="L2" s="4"/>
-      <x:c r="M2" s="4"/>
-      <x:c r="N2" s="4"/>
-      <x:c r="O2" s="4"/>
-      <x:c r="P2" s="4"/>
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="B2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="C2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="D2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="E2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="F2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="G2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="H2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="I2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="J2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="K2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="L2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="M2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="N2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="O2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
+      <x:c r="P2" s="4" t="str">
+        <x:v>Selected NIST CSF 2.0 outcomes based on Trainory's risk and assessment scope</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="6" t="str">
@@ -976,9 +1049,7 @@
       <x:c r="N13" s="47" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O13" s="41" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O13" s="41"/>
       <x:c r="P13" s="41" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1026,9 +1097,7 @@
       <x:c r="N14" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O14" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O14" s="42"/>
       <x:c r="P14" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1076,9 +1145,7 @@
       <x:c r="N15" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O15" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O15" s="42"/>
       <x:c r="P15" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1126,9 +1193,7 @@
       <x:c r="N16" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O16" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O16" s="42"/>
       <x:c r="P16" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1176,9 +1241,7 @@
       <x:c r="N17" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O17" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O17" s="42"/>
       <x:c r="P17" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1226,9 +1289,7 @@
       <x:c r="N18" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O18" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O18" s="42"/>
       <x:c r="P18" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1276,9 +1337,7 @@
       <x:c r="N19" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O19" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O19" s="42"/>
       <x:c r="P19" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1326,9 +1385,7 @@
       <x:c r="N20" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O20" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O20" s="42"/>
       <x:c r="P20" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1376,9 +1433,7 @@
       <x:c r="N21" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O21" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O21" s="42"/>
       <x:c r="P21" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1426,9 +1481,7 @@
       <x:c r="N22" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O22" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O22" s="42"/>
       <x:c r="P22" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1476,9 +1529,7 @@
       <x:c r="N23" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O23" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O23" s="42"/>
       <x:c r="P23" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1526,9 +1577,7 @@
       <x:c r="N24" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O24" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O24" s="42"/>
       <x:c r="P24" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1576,9 +1625,7 @@
       <x:c r="N25" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O25" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O25" s="42"/>
       <x:c r="P25" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1626,9 +1673,7 @@
       <x:c r="N26" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O26" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O26" s="42"/>
       <x:c r="P26" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1676,9 +1721,7 @@
       <x:c r="N27" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O27" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O27" s="42"/>
       <x:c r="P27" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1726,9 +1769,7 @@
       <x:c r="N28" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O28" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O28" s="42"/>
       <x:c r="P28" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1776,9 +1817,7 @@
       <x:c r="N29" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O29" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O29" s="42"/>
       <x:c r="P29" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1826,9 +1865,7 @@
       <x:c r="N30" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O30" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O30" s="42"/>
       <x:c r="P30" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1876,9 +1913,7 @@
       <x:c r="N31" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O31" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O31" s="42"/>
       <x:c r="P31" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1926,9 +1961,7 @@
       <x:c r="N32" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O32" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O32" s="42"/>
       <x:c r="P32" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -1976,9 +2009,7 @@
       <x:c r="N33" s="48" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O33" s="42" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O33" s="42"/>
       <x:c r="P33" s="42" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -2026,9 +2057,7 @@
       <x:c r="N34" s="49" t="str">
         <x:v>Pending review</x:v>
       </x:c>
-      <x:c r="O34" s="43" t="str">
-        <x:v>Fictional assessment; validate evidence and ownership.</x:v>
-      </x:c>
+      <x:c r="O34" s="43"/>
       <x:c r="P34" s="43" t="str">
         <x:v>https://www.nist.gov/cyberframework</x:v>
       </x:c>
@@ -2068,7 +2097,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R456b5be9f7fb4105"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c8e37c79bd9459a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2084,14 +2113,22 @@
     <x:col min="6" max="6" width="26" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="2" t="str">
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="96" t="str">
         <x:v>Trainory Framework Guide</x:v>
       </x:c>
-      <x:c r="B1" s="2"/>
-      <x:c r="C1" s="2"/>
-      <x:c r="D1" s="2"/>
-      <x:c r="E1" s="2"/>
+      <x:c r="B1" s="96" t="str">
+        <x:v>Trainory Framework Guide</x:v>
+      </x:c>
+      <x:c r="C1" s="96" t="str">
+        <x:v>Trainory Framework Guide</x:v>
+      </x:c>
+      <x:c r="D1" s="96" t="str">
+        <x:v>Trainory Framework Guide</x:v>
+      </x:c>
+      <x:c r="E1" s="96" t="str">
+        <x:v>Trainory Framework Guide</x:v>
+      </x:c>
       <x:c r="F1" s="2"/>
     </x:row>
     <x:row r="3">
@@ -2101,9 +2138,7 @@
       <x:c r="B3" s="6" t="str">
         <x:v>Plain-language purpose</x:v>
       </x:c>
-      <x:c r="D3" s="60" t="str">
-        <x:v>How to explain this in an interview</x:v>
-      </x:c>
+      <x:c r="D3" s="60"/>
       <x:c r="E3" s="60"/>
       <x:c r="F3" s="60"/>
     </x:row>
@@ -2114,9 +2149,7 @@
       <x:c r="B4" s="54" t="str">
         <x:v>Set direction, responsibilities, policies, and oversight.</x:v>
       </x:c>
-      <x:c r="D4" s="79" t="str">
-        <x:v>I used NIST CSF 2.0 to organize Trainory's desired cybersecurity outcomes across Govern, Identify, Protect, Detect, Respond, and Recover. I assessed selected outcomes that directly relate to the company's assets and risks, documented assumed evidence, identified gaps, and recommended practical actions. I also listed selected NIST SP 800-53 controls as examples for deeper control-level work; they are not presented as a formal certification or complete crosswalk.</x:v>
-      </x:c>
+      <x:c r="D4" s="79"/>
       <x:c r="E4" s="80"/>
       <x:c r="F4" s="81"/>
     </x:row>
@@ -2217,13 +2250,13 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="D3:F3"/>
     <x:mergeCell ref="D4:F9"/>
     <x:mergeCell ref="A11:F11"/>
     <x:mergeCell ref="A12:F12"/>
     <x:mergeCell ref="A13:F13"/>
     <x:mergeCell ref="A14:F14"/>
+    <x:mergeCell ref="A1:E1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
